--- a/document/31条指令操作时间表.xlsx
+++ b/document/31条指令操作时间表.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\github\cpu31\document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCB44C20-A195-460F-A37F-73BB0745FE97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03E9F312-8FC1-47C9-9E50-082E1BBB5FFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{7CAB809C-24DC-4464-89F1-2B336DD29E79}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="1" xr2:uid="{7CAB809C-24DC-4464-89F1-2B336DD29E79}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="815" uniqueCount="241">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1125" uniqueCount="241">
   <si>
     <t>cpu指令集</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -3450,989 +3450,1044 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="A2" s="4" t="s">
         <v>102</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="H2" t="s">
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
         <v>104</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="4" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="A3" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="4" t="s">
         <v>108</v>
       </c>
-      <c r="C3" t="s">
+      <c r="C3" s="4" t="s">
         <v>109</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="4" t="s">
         <v>110</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="4" t="s">
         <v>111</v>
       </c>
-      <c r="F3" t="s">
+      <c r="F3" s="4" t="s">
         <v>112</v>
       </c>
-      <c r="G3" t="s">
+      <c r="G3" s="4" t="s">
         <v>113</v>
       </c>
+      <c r="H3" s="4"/>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="A4" s="4" t="s">
         <v>114</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C4" t="s">
+      <c r="C4" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F4" t="s">
+      <c r="F4" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="G4" t="s">
+      <c r="G4" s="4" t="s">
         <v>120</v>
       </c>
+      <c r="H4" s="4"/>
+      <c r="I4" s="4"/>
+      <c r="J4" s="4"/>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="A5" s="4" t="s">
         <v>121</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="4">
         <v>0</v>
       </c>
-      <c r="C5" t="s">
+      <c r="G5" s="4">
+        <v>100000</v>
+      </c>
+      <c r="H5" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A6" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C6" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D6" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E6" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F5">
+      <c r="F6" s="4">
         <v>0</v>
       </c>
-      <c r="G5">
-        <v>100000</v>
-      </c>
-      <c r="H5" t="s">
-        <v>122</v>
-      </c>
-      <c r="I5" t="s">
+      <c r="G6" s="4">
+        <v>100001</v>
+      </c>
+      <c r="H6" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="I6" s="4" t="s">
         <v>123</v>
       </c>
-      <c r="J5" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>125</v>
-      </c>
-      <c r="B6">
+      <c r="J6" s="4" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F7" s="4">
         <v>0</v>
       </c>
-      <c r="C6" t="s">
+      <c r="G7" s="4">
+        <v>100010</v>
+      </c>
+      <c r="H7" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="J7" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A8" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C8" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D8" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E8" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F6">
+      <c r="F8" s="4">
         <v>0</v>
       </c>
-      <c r="G6">
-        <v>100001</v>
-      </c>
-      <c r="H6" t="s">
-        <v>126</v>
-      </c>
-      <c r="I6" t="s">
-        <v>123</v>
-      </c>
-      <c r="J6" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>128</v>
-      </c>
-      <c r="B7">
+      <c r="G8" s="4">
+        <v>100011</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A9" s="4" t="s">
+        <v>135</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E9" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F9" s="4">
         <v>0</v>
       </c>
-      <c r="C7" t="s">
+      <c r="G9" s="4">
+        <v>100100</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="J9" s="4" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A10" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C10" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D10" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E10" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F7">
+      <c r="F10" s="4">
         <v>0</v>
       </c>
-      <c r="G7">
-        <v>100010</v>
-      </c>
-      <c r="H7" t="s">
-        <v>129</v>
-      </c>
-      <c r="I7" t="s">
-        <v>130</v>
-      </c>
-      <c r="J7" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>132</v>
-      </c>
-      <c r="B8">
+      <c r="G10" s="4">
+        <v>100101</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="J10" s="4" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A11" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F11" s="4">
         <v>0</v>
       </c>
-      <c r="C8" t="s">
+      <c r="G11" s="4">
+        <v>100110</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C12" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D12" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E12" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="F8">
+      <c r="F12" s="4">
         <v>0</v>
       </c>
-      <c r="G8">
+      <c r="G12" s="4">
+        <v>100111</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>149</v>
+      </c>
+      <c r="J12" s="4" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A13" s="4" t="s">
+        <v>151</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F13" s="4">
+        <v>0</v>
+      </c>
+      <c r="G13" s="4">
+        <v>101010</v>
+      </c>
+      <c r="H13" s="4" t="s">
+        <v>152</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A14" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F14" s="4">
+        <v>0</v>
+      </c>
+      <c r="G14" s="4">
+        <v>101011</v>
+      </c>
+      <c r="H14" s="4" t="s">
+        <v>155</v>
+      </c>
+      <c r="I14" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C15" s="4">
+        <v>0</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G15" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="H15" s="4" t="s">
+        <v>157</v>
+      </c>
+      <c r="I15" s="4" t="s">
+        <v>158</v>
+      </c>
+      <c r="J15" s="4" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A16" s="4" t="s">
+        <v>159</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C16" s="4">
+        <v>0</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G16" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="H16" s="4" t="s">
+        <v>160</v>
+      </c>
+      <c r="I16" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="J16" s="4" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C17" s="4">
+        <v>0</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>119</v>
+      </c>
+      <c r="G17" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="H17" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="I17" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="J17" s="4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A18" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F18" s="4">
+        <v>0</v>
+      </c>
+      <c r="G18" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="H18" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="I18" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="J18" s="4" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A19" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F19" s="4">
+        <v>0</v>
+      </c>
+      <c r="G19" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H19" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="I19" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="J19" s="4" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A20" s="4" t="s">
+        <v>173</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F20" s="4">
+        <v>0</v>
+      </c>
+      <c r="G20" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="H20" s="4" t="s">
+        <v>174</v>
+      </c>
+      <c r="I20" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A21" s="4" t="s">
+        <v>175</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D21" s="4">
+        <v>0</v>
+      </c>
+      <c r="E21" s="4">
+        <v>0</v>
+      </c>
+      <c r="F21" s="4">
+        <v>0</v>
+      </c>
+      <c r="G21" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="H21" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="I21" s="4" t="s">
+        <v>177</v>
+      </c>
+      <c r="J21" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A22" s="4" t="s">
+        <v>179</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F22" s="4"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="4"/>
+      <c r="I22" s="4"/>
+      <c r="J22" s="4"/>
+    </row>
+    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A23" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="I23" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="J23" s="4" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A24" s="4" t="s">
+        <v>185</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F24" s="4"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="I24" s="4" t="s">
+        <v>183</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A25" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F25" s="4"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I25" s="4" t="s">
+        <v>190</v>
+      </c>
+      <c r="J25" s="4" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F26" s="4"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I26" s="4" t="s">
+        <v>193</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A27" s="4" t="s">
+        <v>195</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F27" s="4"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="4" t="s">
+        <v>189</v>
+      </c>
+      <c r="I27" s="4" t="s">
+        <v>196</v>
+      </c>
+      <c r="J27" s="4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="C28" s="4">
+        <v>0</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F28" s="4"/>
+      <c r="G28" s="4"/>
+      <c r="H28" s="4" t="s">
+        <v>199</v>
+      </c>
+      <c r="I28" s="4" t="s">
+        <v>200</v>
+      </c>
+      <c r="J28" s="4" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B29" s="4">
         <v>100011</v>
       </c>
-      <c r="H8" t="s">
-        <v>133</v>
-      </c>
-      <c r="I8" t="s">
-        <v>130</v>
-      </c>
-      <c r="J8" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>135</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-      <c r="C9" t="s">
+      <c r="C29" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D29" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E9" t="s">
-        <v>118</v>
-      </c>
-      <c r="F9">
-        <v>0</v>
-      </c>
-      <c r="G9">
-        <v>100100</v>
-      </c>
-      <c r="H9" t="s">
-        <v>136</v>
-      </c>
-      <c r="I9" t="s">
-        <v>137</v>
-      </c>
-      <c r="J9" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>139</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-      <c r="C10" t="s">
+      <c r="E29" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F29" s="4"/>
+      <c r="G29" s="4"/>
+      <c r="H29" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="I29" s="4" t="s">
+        <v>231</v>
+      </c>
+      <c r="J29" s="4" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A30" s="4" t="s">
+        <v>204</v>
+      </c>
+      <c r="B30" s="4">
+        <v>101011</v>
+      </c>
+      <c r="C30" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D30" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E10" t="s">
-        <v>118</v>
-      </c>
-      <c r="F10">
-        <v>0</v>
-      </c>
-      <c r="G10">
-        <v>100101</v>
-      </c>
-      <c r="H10" t="s">
-        <v>140</v>
-      </c>
-      <c r="I10" t="s">
-        <v>141</v>
-      </c>
-      <c r="J10" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>143</v>
-      </c>
-      <c r="B11">
-        <v>0</v>
-      </c>
-      <c r="C11" t="s">
+      <c r="E30" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F30" s="4"/>
+      <c r="G30" s="4"/>
+      <c r="H30" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="I30" s="4" t="s">
+        <v>232</v>
+      </c>
+      <c r="J30" s="4" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>207</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C31" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D31" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E11" t="s">
-        <v>118</v>
-      </c>
-      <c r="F11">
-        <v>0</v>
-      </c>
-      <c r="G11">
-        <v>100110</v>
-      </c>
-      <c r="H11" t="s">
-        <v>144</v>
-      </c>
-      <c r="I11" t="s">
-        <v>145</v>
-      </c>
-      <c r="J11" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>147</v>
-      </c>
-      <c r="B12">
-        <v>0</v>
-      </c>
-      <c r="C12" t="s">
+      <c r="E31" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F31" s="4"/>
+      <c r="G31" s="4"/>
+      <c r="H31" s="4" t="s">
+        <v>208</v>
+      </c>
+      <c r="I31" s="4" t="s">
+        <v>233</v>
+      </c>
+      <c r="J31" s="4" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="C32" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D32" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E12" t="s">
-        <v>118</v>
-      </c>
-      <c r="F12">
-        <v>0</v>
-      </c>
-      <c r="G12">
-        <v>100111</v>
-      </c>
-      <c r="H12" t="s">
-        <v>148</v>
-      </c>
-      <c r="I12" t="s">
-        <v>149</v>
-      </c>
-      <c r="J12" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>151</v>
-      </c>
-      <c r="B13">
-        <v>0</v>
-      </c>
-      <c r="C13" t="s">
+      <c r="E32" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F32" s="4"/>
+      <c r="G32" s="4"/>
+      <c r="H32" s="4" t="s">
+        <v>211</v>
+      </c>
+      <c r="I32" s="4" t="s">
+        <v>234</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
+        <v>213</v>
+      </c>
+      <c r="B33" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C33" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D33" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E13" t="s">
-        <v>118</v>
-      </c>
-      <c r="F13">
-        <v>0</v>
-      </c>
-      <c r="G13">
-        <v>101010</v>
-      </c>
-      <c r="H13" t="s">
-        <v>152</v>
-      </c>
-      <c r="I13" t="s">
-        <v>225</v>
-      </c>
-      <c r="J13" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A14" t="s">
-        <v>154</v>
-      </c>
-      <c r="B14">
-        <v>0</v>
-      </c>
-      <c r="C14" t="s">
+      <c r="E33" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F33" s="4"/>
+      <c r="G33" s="4"/>
+      <c r="H33" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="I33" s="4" t="s">
+        <v>235</v>
+      </c>
+      <c r="J33" s="4" t="s">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A34" s="4" t="s">
+        <v>215</v>
+      </c>
+      <c r="B34" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C34" s="4" t="s">
         <v>116</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D34" s="4" t="s">
         <v>117</v>
       </c>
-      <c r="E14" t="s">
-        <v>118</v>
-      </c>
-      <c r="F14">
-        <v>0</v>
-      </c>
-      <c r="G14">
-        <v>101011</v>
-      </c>
-      <c r="H14" t="s">
-        <v>155</v>
-      </c>
-      <c r="I14" t="s">
-        <v>225</v>
-      </c>
-      <c r="J14" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>156</v>
-      </c>
-      <c r="B15">
-        <v>0</v>
-      </c>
-      <c r="C15">
-        <v>0</v>
-      </c>
-      <c r="D15" t="s">
-        <v>117</v>
-      </c>
-      <c r="E15" t="s">
-        <v>118</v>
-      </c>
-      <c r="F15" t="s">
-        <v>119</v>
-      </c>
-      <c r="G15">
-        <v>0</v>
-      </c>
-      <c r="H15" t="s">
-        <v>157</v>
-      </c>
-      <c r="I15" t="s">
-        <v>158</v>
-      </c>
-      <c r="J15" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>159</v>
-      </c>
-      <c r="B16">
-        <v>0</v>
-      </c>
-      <c r="C16">
-        <v>0</v>
-      </c>
-      <c r="D16" t="s">
-        <v>117</v>
-      </c>
-      <c r="E16" t="s">
-        <v>118</v>
-      </c>
-      <c r="F16" t="s">
-        <v>119</v>
-      </c>
-      <c r="G16">
-        <v>10</v>
-      </c>
-      <c r="H16" t="s">
-        <v>160</v>
-      </c>
-      <c r="I16" t="s">
-        <v>161</v>
-      </c>
-      <c r="J16" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>163</v>
-      </c>
-      <c r="B17">
-        <v>0</v>
-      </c>
-      <c r="C17">
-        <v>0</v>
-      </c>
-      <c r="D17" t="s">
-        <v>117</v>
-      </c>
-      <c r="E17" t="s">
-        <v>118</v>
-      </c>
-      <c r="F17" t="s">
-        <v>119</v>
-      </c>
-      <c r="G17">
-        <v>11</v>
-      </c>
-      <c r="H17" t="s">
-        <v>164</v>
-      </c>
-      <c r="I17" t="s">
-        <v>161</v>
-      </c>
-      <c r="J17" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>165</v>
-      </c>
-      <c r="B18">
-        <v>0</v>
-      </c>
-      <c r="C18" t="s">
-        <v>116</v>
-      </c>
-      <c r="D18" t="s">
-        <v>117</v>
-      </c>
-      <c r="E18" t="s">
-        <v>118</v>
-      </c>
-      <c r="F18">
-        <v>0</v>
-      </c>
-      <c r="G18">
-        <v>100</v>
-      </c>
-      <c r="H18" t="s">
-        <v>166</v>
-      </c>
-      <c r="I18" t="s">
-        <v>167</v>
-      </c>
-      <c r="J18" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>169</v>
-      </c>
-      <c r="B19">
-        <v>0</v>
-      </c>
-      <c r="C19" t="s">
-        <v>116</v>
-      </c>
-      <c r="D19" t="s">
-        <v>117</v>
-      </c>
-      <c r="E19" t="s">
-        <v>118</v>
-      </c>
-      <c r="F19">
-        <v>0</v>
-      </c>
-      <c r="G19">
-        <v>110</v>
-      </c>
-      <c r="H19" t="s">
-        <v>170</v>
-      </c>
-      <c r="I19" t="s">
-        <v>171</v>
-      </c>
-      <c r="J19" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
-        <v>173</v>
-      </c>
-      <c r="B20">
-        <v>0</v>
-      </c>
-      <c r="C20" t="s">
-        <v>116</v>
-      </c>
-      <c r="D20" t="s">
-        <v>117</v>
-      </c>
-      <c r="E20" t="s">
-        <v>118</v>
-      </c>
-      <c r="F20">
-        <v>0</v>
-      </c>
-      <c r="G20">
-        <v>111</v>
-      </c>
-      <c r="H20" t="s">
-        <v>174</v>
-      </c>
-      <c r="I20" t="s">
-        <v>171</v>
-      </c>
-      <c r="J20" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
-        <v>175</v>
-      </c>
-      <c r="B21">
-        <v>0</v>
-      </c>
-      <c r="C21" t="s">
-        <v>116</v>
-      </c>
-      <c r="D21">
-        <v>0</v>
-      </c>
-      <c r="E21">
-        <v>0</v>
-      </c>
-      <c r="F21">
-        <v>0</v>
-      </c>
-      <c r="G21">
-        <v>1000</v>
-      </c>
-      <c r="H21" t="s">
-        <v>176</v>
-      </c>
-      <c r="I21" t="s">
-        <v>177</v>
-      </c>
-      <c r="J21" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A22" t="s">
-        <v>179</v>
-      </c>
-      <c r="B22" t="s">
+      <c r="E34" s="4" t="s">
+        <v>180</v>
+      </c>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+      <c r="H34" s="4" t="s">
+        <v>216</v>
+      </c>
+      <c r="I34" s="4" t="s">
+        <v>237</v>
+      </c>
+      <c r="J34" s="4" t="s">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A35" s="4" t="s">
+        <v>217</v>
+      </c>
+      <c r="B35" s="4" t="s">
         <v>115</v>
       </c>
-      <c r="C22" t="s">
-        <v>116</v>
-      </c>
-      <c r="D22" t="s">
-        <v>117</v>
-      </c>
-      <c r="E22" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A23" t="s">
-        <v>181</v>
-      </c>
-      <c r="B23">
-        <v>1000</v>
-      </c>
-      <c r="C23" t="s">
-        <v>116</v>
-      </c>
-      <c r="D23" t="s">
-        <v>117</v>
-      </c>
-      <c r="E23" t="s">
-        <v>180</v>
-      </c>
-      <c r="H23" t="s">
-        <v>182</v>
-      </c>
-      <c r="I23" t="s">
-        <v>183</v>
-      </c>
-      <c r="J23" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
-        <v>185</v>
-      </c>
-      <c r="B24">
-        <v>1001</v>
-      </c>
-      <c r="C24" t="s">
-        <v>116</v>
-      </c>
-      <c r="D24" t="s">
-        <v>117</v>
-      </c>
-      <c r="E24" t="s">
-        <v>180</v>
-      </c>
-      <c r="H24" t="s">
-        <v>186</v>
-      </c>
-      <c r="I24" t="s">
-        <v>183</v>
-      </c>
-      <c r="J24" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A25" t="s">
-        <v>188</v>
-      </c>
-      <c r="B25">
-        <v>1100</v>
-      </c>
-      <c r="C25" t="s">
-        <v>116</v>
-      </c>
-      <c r="D25" t="s">
-        <v>117</v>
-      </c>
-      <c r="E25" t="s">
-        <v>180</v>
-      </c>
-      <c r="H25" t="s">
-        <v>189</v>
-      </c>
-      <c r="I25" t="s">
-        <v>190</v>
-      </c>
-      <c r="J25" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A26" t="s">
-        <v>192</v>
-      </c>
-      <c r="B26">
-        <v>1101</v>
-      </c>
-      <c r="C26" t="s">
-        <v>116</v>
-      </c>
-      <c r="D26" t="s">
-        <v>117</v>
-      </c>
-      <c r="E26" t="s">
-        <v>180</v>
-      </c>
-      <c r="H26" t="s">
-        <v>189</v>
-      </c>
-      <c r="I26" t="s">
-        <v>193</v>
-      </c>
-      <c r="J26" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>195</v>
-      </c>
-      <c r="B27">
-        <v>1110</v>
-      </c>
-      <c r="C27" t="s">
-        <v>116</v>
-      </c>
-      <c r="D27" t="s">
-        <v>117</v>
-      </c>
-      <c r="E27" t="s">
-        <v>180</v>
-      </c>
-      <c r="H27" t="s">
-        <v>189</v>
-      </c>
-      <c r="I27" t="s">
-        <v>196</v>
-      </c>
-      <c r="J27" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>198</v>
-      </c>
-      <c r="B28">
-        <v>1111</v>
-      </c>
-      <c r="C28">
-        <v>0</v>
-      </c>
-      <c r="D28" t="s">
-        <v>117</v>
-      </c>
-      <c r="E28" t="s">
-        <v>180</v>
-      </c>
-      <c r="H28" t="s">
-        <v>199</v>
-      </c>
-      <c r="I28" t="s">
-        <v>200</v>
-      </c>
-      <c r="J28" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A29" t="s">
-        <v>201</v>
-      </c>
-      <c r="B29">
-        <v>100011</v>
-      </c>
-      <c r="C29" t="s">
-        <v>116</v>
-      </c>
-      <c r="D29" t="s">
-        <v>117</v>
-      </c>
-      <c r="E29" t="s">
-        <v>180</v>
-      </c>
-      <c r="H29" t="s">
-        <v>202</v>
-      </c>
-      <c r="I29" t="s">
-        <v>231</v>
-      </c>
-      <c r="J29" t="s">
-        <v>203</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>204</v>
-      </c>
-      <c r="B30">
-        <v>101011</v>
-      </c>
-      <c r="C30" t="s">
-        <v>116</v>
-      </c>
-      <c r="D30" t="s">
-        <v>117</v>
-      </c>
-      <c r="E30" t="s">
-        <v>180</v>
-      </c>
-      <c r="H30" t="s">
-        <v>205</v>
-      </c>
-      <c r="I30" t="s">
-        <v>232</v>
-      </c>
-      <c r="J30" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>207</v>
-      </c>
-      <c r="B31">
-        <v>100</v>
-      </c>
-      <c r="C31" t="s">
-        <v>116</v>
-      </c>
-      <c r="D31" t="s">
-        <v>117</v>
-      </c>
-      <c r="E31" t="s">
-        <v>180</v>
-      </c>
-      <c r="H31" t="s">
-        <v>208</v>
-      </c>
-      <c r="I31" t="s">
-        <v>233</v>
-      </c>
-      <c r="J31" t="s">
-        <v>209</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>210</v>
-      </c>
-      <c r="B32">
-        <v>101</v>
-      </c>
-      <c r="C32" t="s">
-        <v>116</v>
-      </c>
-      <c r="D32" t="s">
-        <v>117</v>
-      </c>
-      <c r="E32" t="s">
-        <v>180</v>
-      </c>
-      <c r="H32" t="s">
-        <v>211</v>
-      </c>
-      <c r="I32" t="s">
-        <v>234</v>
-      </c>
-      <c r="J32" t="s">
-        <v>212</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A33" t="s">
-        <v>213</v>
-      </c>
-      <c r="B33">
-        <v>1010</v>
-      </c>
-      <c r="C33" t="s">
-        <v>116</v>
-      </c>
-      <c r="D33" t="s">
-        <v>117</v>
-      </c>
-      <c r="E33" t="s">
-        <v>180</v>
-      </c>
-      <c r="H33" t="s">
-        <v>214</v>
-      </c>
-      <c r="I33" t="s">
-        <v>235</v>
-      </c>
-      <c r="J33" t="s">
-        <v>236</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
-        <v>215</v>
-      </c>
-      <c r="B34">
-        <v>1011</v>
-      </c>
-      <c r="C34" t="s">
-        <v>116</v>
-      </c>
-      <c r="D34" t="s">
-        <v>117</v>
-      </c>
-      <c r="E34" t="s">
-        <v>180</v>
-      </c>
-      <c r="H34" t="s">
-        <v>216</v>
-      </c>
-      <c r="I34" t="s">
-        <v>237</v>
-      </c>
-      <c r="J34" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A35" t="s">
-        <v>217</v>
-      </c>
-      <c r="B35" t="s">
-        <v>115</v>
-      </c>
-      <c r="C35" t="s">
+      <c r="C35" s="4" t="s">
         <v>218</v>
       </c>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
+      <c r="A36" s="4" t="s">
         <v>219</v>
       </c>
-      <c r="B36">
-        <v>10</v>
-      </c>
-      <c r="C36" t="s">
+      <c r="B36" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C36" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="H36" t="s">
+      <c r="D36" s="4"/>
+      <c r="E36" s="4"/>
+      <c r="F36" s="4"/>
+      <c r="G36" s="4"/>
+      <c r="H36" s="4" t="s">
         <v>220</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I36" s="4" t="s">
         <v>221</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J36" s="4" t="s">
         <v>222</v>
       </c>
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
+      <c r="A37" s="4" t="s">
         <v>223</v>
       </c>
-      <c r="B37">
-        <v>11</v>
-      </c>
-      <c r="C37" t="s">
+      <c r="B37" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="C37" s="4" t="s">
         <v>218</v>
       </c>
-      <c r="H37" t="s">
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4" t="s">
         <v>224</v>
       </c>
-      <c r="I37" t="s">
+      <c r="I37" s="4" t="s">
         <v>239</v>
       </c>
-      <c r="J37" t="s">
+      <c r="J37" s="4" t="s">
         <v>240</v>
       </c>
     </row>
